--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37885-2026 artfynd.xlsx
+++ b/artfynd/A 37885-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439495</v>
       </c>
       <c r="B2" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
